--- a/input/timetable/Магистратура_Лингвистика_xlsx.xlsx
+++ b/input/timetable/Магистратура_Лингвистика_xlsx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="24" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="69">
   <si>
     <t>пара</t>
   </si>
@@ -69,6 +69,9 @@
     <t>Директор института</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -108,15 +111,24 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Чмых И.Е.</t>
+  </si>
+  <si>
     <t>Основы научных исследований в области лингвистики и лингводидактики (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Король Е.В.</t>
+  </si>
+  <si>
     <t>Актуальные проблемы английского языкознания (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Актуальные проблемы английского языкознания (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Коптякова Е.Е.</t>
+  </si>
+  <si>
     <t>208-41м</t>
   </si>
   <si>
@@ -129,6 +141,9 @@
     <t>ЭУК</t>
   </si>
   <si>
+    <t>Король Е.В</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
@@ -159,6 +174,12 @@
     <t>20.02.2026 - 04.04.2026</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Марданова М.А.</t>
+  </si>
+  <si>
     <t>Актуальные проблемы перевода (лек), ЭОиДОТ</t>
   </si>
   <si>
@@ -168,6 +189,9 @@
     <t>Практический курс перевода английского языка (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Назин А.С.</t>
+  </si>
+  <si>
     <t>Учебная практика, переводческая практика, ЭОиДОТ//</t>
   </si>
   <si>
@@ -177,19 +201,31 @@
     <t>Академическое письмо (английский язык) (пр), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Сало В.Э.</t>
+  </si>
+  <si>
     <t>Деловой английский язык (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Добрынина О.В.</t>
+  </si>
+  <si>
     <t>Лингводидактика и дистанционные образовательные технологии в высшей школе (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Лингводидактика и дистанционные образовательные технологии в высшей школе (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Коптякова Е.Е</t>
+  </si>
+  <si>
     <t>Производственная практика, научно-исследовательская работа, ЭОиДОТ//</t>
   </si>
   <si>
     <t>// История и методология науки (пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Курбанов И.А.</t>
   </si>
 </sst>
 </file>
@@ -290,7 +326,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,8 +343,14 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="48">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -388,6 +430,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -461,6 +561,19 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -767,6 +880,17 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -902,6 +1026,15 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -913,7 +1046,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -956,28 +1089,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1005,7 +1141,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1019,198 +1155,215 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -1519,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1528,10 +1681,11 @@
     <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1539,15 +1693,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1555,13 +1709,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1571,27 +1725,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="37" t="s">
-        <v>17</v>
+      <c r="C7" s="38" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -1601,46 +1755,46 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="39" t="s">
-        <v>39</v>
+      <c r="D8" s="39"/>
+      <c r="E8" s="40" t="s">
+        <v>44</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
+        <v>26</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
       <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
+        <v>29</v>
+      </c>
+      <c r="C10" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
       <c r="F10" s="17"/>
     </row>
-    <row r="11" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>0</v>
@@ -1651,233 +1805,279 @@
       <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="35">
+      <c r="G11" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="36">
         <v>6</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
-      <c r="O12" s="53"/>
-    </row>
-    <row r="13" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="C12" s="81"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="65"/>
+      <c r="P12" s="58"/>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>7</v>
       </c>
-      <c r="C13" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="60"/>
-    </row>
-    <row r="14" spans="1:15" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="100" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>8</v>
       </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="63"/>
-    </row>
-    <row r="15" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="C14" s="103"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="52"/>
+    </row>
+    <row r="15" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="26">
         <v>6</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="81"/>
-    </row>
-    <row r="16" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="C15" s="87"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="59"/>
+    </row>
+    <row r="16" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>7</v>
       </c>
-      <c r="C16" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="66"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="31"/>
-      <c r="B17" s="29">
+      <c r="C16" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="32"/>
+      <c r="B17" s="30">
         <v>8</v>
       </c>
-      <c r="C17" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="57"/>
-    </row>
-    <row r="18" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="C17" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="67" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="26">
         <v>6</v>
       </c>
-      <c r="C18" s="88"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="90"/>
-    </row>
-    <row r="19" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="C18" s="78"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="60"/>
+    </row>
+    <row r="19" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>7</v>
       </c>
-      <c r="C19" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="31"/>
-      <c r="B20" s="29">
+      <c r="C19" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="62" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="32"/>
+      <c r="B20" s="30">
         <v>8</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="109" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="26">
+        <v>6</v>
+      </c>
+      <c r="C21" s="112"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="65"/>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
+        <v>7</v>
+      </c>
+      <c r="C22" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="97"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="32"/>
+      <c r="B23" s="30">
+        <v>8</v>
+      </c>
+      <c r="C23" s="93" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="67" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="26">
+        <v>6</v>
+      </c>
+      <c r="C24" s="87"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="65"/>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="33"/>
+      <c r="B25" s="28">
+        <v>7</v>
+      </c>
+      <c r="C25" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="34"/>
+      <c r="B26" s="30">
+        <v>8</v>
+      </c>
+      <c r="C26" s="93" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="94"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="67" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="36">
+        <v>2</v>
+      </c>
+      <c r="C27" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="25">
-        <v>6</v>
-      </c>
-      <c r="C21" s="73"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="75"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
-        <v>7</v>
-      </c>
-      <c r="C22" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="78"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="31"/>
-      <c r="B23" s="29">
-        <v>8</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="57"/>
-    </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="25">
-        <v>6</v>
-      </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="81"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="32"/>
-      <c r="B25" s="27">
-        <v>7</v>
-      </c>
-      <c r="C25" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="29">
-        <v>8</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
-    </row>
-    <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="35">
-        <v>2</v>
-      </c>
-      <c r="C27" s="82" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
-    </row>
-    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
-    </row>
-    <row r="29" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="49"/>
-      <c r="B29" s="50">
+    </row>
+    <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="33"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="70"/>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="54"/>
+      <c r="B29" s="55">
         <v>5</v>
       </c>
-      <c r="C29" s="85" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="86"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="87"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="51"/>
-      <c r="B30" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="96"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C29" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="71" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="56"/>
+      <c r="B30" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="84" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
@@ -1887,23 +2087,14 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C13:F13"/>
@@ -1915,6 +2106,15 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:E9 C10">
     <cfRule type="expression" priority="2">
@@ -1942,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1951,10 +2151,11 @@
     <col min="4" max="4" width="19.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1962,15 +2163,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1978,13 +2179,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1994,27 +2195,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="37" t="s">
-        <v>17</v>
+      <c r="C7" s="38" t="s">
+        <v>18</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -2024,275 +2225,307 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="53"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K8" s="58"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>44</v>
+        <v>26</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>49</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>45</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>50</v>
       </c>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
     </row>
-    <row r="11" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44"/>
-    </row>
-    <row r="12" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="25">
+      <c r="D11" s="43"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="26">
         <v>6</v>
       </c>
-      <c r="C12" s="97" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
-    </row>
-    <row r="13" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="45">
+      <c r="C12" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="68"/>
+    </row>
+    <row r="13" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="46">
         <v>7</v>
       </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="78"/>
-    </row>
-    <row r="14" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="96"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="66"/>
+    </row>
+    <row r="14" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>8</v>
       </c>
-      <c r="C14" s="100"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="102"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="C14" s="127"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="67"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A15" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="26">
         <v>6</v>
       </c>
-      <c r="C15" s="103"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="105"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="C15" s="130"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="60"/>
+    </row>
+    <row r="16" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>7</v>
       </c>
-      <c r="C16" s="76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="78"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="31"/>
-      <c r="B17" s="29">
+      <c r="C16" s="96" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="66" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="32"/>
+      <c r="B17" s="30">
         <v>8</v>
       </c>
-      <c r="C17" s="100" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="C17" s="127" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="67" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="26">
         <v>6</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="75"/>
-    </row>
-    <row r="19" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="C18" s="112"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="68"/>
+    </row>
+    <row r="19" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>7</v>
       </c>
-      <c r="C19" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
-    </row>
-    <row r="20" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="31"/>
-      <c r="B20" s="29">
+      <c r="C19" s="96" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="69" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="32"/>
+      <c r="B20" s="30">
         <v>8</v>
       </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="57"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="25">
+      <c r="C20" s="93"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="67"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="26">
         <v>6</v>
       </c>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="99"/>
-    </row>
-    <row r="22" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="45">
+      <c r="C21" s="118"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="60"/>
+    </row>
+    <row r="22" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="46">
         <v>7</v>
       </c>
-      <c r="C22" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="78"/>
-    </row>
-    <row r="23" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="31"/>
-      <c r="B23" s="29">
+      <c r="C22" s="96" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="97"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="66" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="32"/>
+      <c r="B23" s="30">
         <v>8</v>
       </c>
-      <c r="C23" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="57"/>
-    </row>
-    <row r="24" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="25">
+      <c r="C23" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="67" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="26">
         <v>6</v>
       </c>
-      <c r="C24" s="97" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="99"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="26"/>
-      <c r="B25" s="45">
+      <c r="C24" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="60"/>
+    </row>
+    <row r="25" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="46">
         <v>7</v>
       </c>
-      <c r="C25" s="112"/>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="114"/>
-    </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="29">
+      <c r="C25" s="124"/>
+      <c r="D25" s="125"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="61"/>
+    </row>
+    <row r="26" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="34"/>
+      <c r="B26" s="30">
         <v>8</v>
       </c>
-      <c r="C26" s="109"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="111"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="25">
+      <c r="C26" s="121"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="52"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="26">
         <v>1</v>
       </c>
-      <c r="C27" s="97" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="99"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="36"/>
-      <c r="B28" s="27">
+      <c r="C27" s="118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="48"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="37"/>
+      <c r="B28" s="28">
         <v>2</v>
       </c>
-      <c r="C28" s="112"/>
-      <c r="D28" s="113"/>
-      <c r="E28" s="113"/>
-      <c r="F28" s="114"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="36"/>
-      <c r="B29" s="27">
+      <c r="C28" s="124"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="53"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="37"/>
+      <c r="B29" s="28">
         <v>3</v>
       </c>
-      <c r="C29" s="112"/>
-      <c r="D29" s="113"/>
-      <c r="E29" s="113"/>
-      <c r="F29" s="114"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="47"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="107"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="108"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C29" s="124"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="53"/>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="49"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="51"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
@@ -2302,21 +2535,14 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C14:F14"/>
@@ -2329,6 +2555,13 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>
